--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_40.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_40.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2387262.717401932</v>
+        <v>2380353.246291292</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9774782.687313257</v>
+        <v>9774782.687313251</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9774782.687313257</v>
+        <v>9774782.687313251</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138604.3777869932</v>
+        <v>138604.37778701</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138604.3777869932</v>
+        <v>138604.37778701</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -739,19 +739,19 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>124.8478761796821</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>127.8837310637179</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>78.1807696284084</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -909,7 +909,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>36.71585008894188</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -976,19 +976,19 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>179.3592314182239</v>
       </c>
       <c r="E6" t="n">
-        <v>12.84202976864526</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1033,7 +1033,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>385</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1146,10 +1146,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>36.71585008894188</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1213,19 +1213,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>175.4172848236332</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>199.8180013219744</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751172319</v>
+        <v>21.95645751173062</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1444,19 +1444,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>81.10557774904923</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H14" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>86.93822665041522</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S15" t="n">
         <v>116.5639999646113</v>
@@ -1750,7 +1750,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1851,7 +1851,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G17" t="n">
         <v>53.75737228701621</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>144.8481678023229</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S18" t="n">
         <v>116.5639999646113</v>
@@ -1975,10 +1975,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U18" t="n">
-        <v>112.8881222856293</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V18" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>82.37314290982852</v>
@@ -2094,7 +2094,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H20" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2161,13 +2161,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>69.86273944538755</v>
+        <v>134.6028150731275</v>
       </c>
       <c r="Y21" t="n">
         <v>49.39139276613435</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2379,7 +2379,7 @@
         <v>288.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>242.2818334606677</v>
+        <v>246.2472248460823</v>
       </c>
       <c r="Y23" t="n">
         <v>161.3174326828064</v>
@@ -2395,7 +2395,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2455,10 +2455,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>132.5405019708301</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y24" t="n">
         <v>49.39139276613435</v>
@@ -2565,7 +2565,7 @@
         <v>86.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>80.25316367243062</v>
+        <v>85.75737228701621</v>
       </c>
       <c r="H26" t="n">
         <v>90.00965870352741</v>
@@ -2619,7 +2619,7 @@
         <v>274.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>193.3174326828064</v>
+        <v>187.8132240682209</v>
       </c>
     </row>
     <row r="27">
@@ -2644,7 +2644,7 @@
         <v>21.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>7.739535875027343</v>
+        <v>7.739535874990011</v>
       </c>
       <c r="H27" t="n">
         <v>14.16808718642113</v>
@@ -2738,28 +2738,28 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>105.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>202.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>253.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>178.0058334593688</v>
+        <v>322.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>369.4478973282775</v>
+        <v>27.10963859936002</v>
       </c>
       <c r="Q28" t="n">
-        <v>407.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>408.6021279811511</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>44.37347970285543</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>86.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>85.75737228701621</v>
+        <v>80.25316367243062</v>
       </c>
       <c r="H29" t="n">
         <v>90.00965870352741</v>
@@ -2856,7 +2856,7 @@
         <v>274.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>187.8132240682209</v>
+        <v>193.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2978,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>202.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>253.1850752716849</v>
       </c>
       <c r="O31" t="n">
         <v>322.445564079015</v>
@@ -2990,10 +2990,10 @@
         <v>369.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>263.3995358059519</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>408.6021279811511</v>
+        <v>216.1849771128682</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>171.3439591878241</v>
+        <v>171.3439591877372</v>
       </c>
       <c r="T32" t="n">
         <v>268.6755817285639</v>
@@ -3154,7 +3154,7 @@
         <v>229.2737972923793</v>
       </c>
       <c r="S33" t="n">
-        <v>148.5639999646113</v>
+        <v>148.5639999645881</v>
       </c>
       <c r="T33" t="n">
         <v>87.35776521751382</v>
@@ -3212,28 +3212,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>105.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>202.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>253.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>322.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>280.2947138710449</v>
       </c>
       <c r="Q34" t="n">
-        <v>407.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>380.4252194180975</v>
+        <v>408.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>44.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3330,7 +3330,7 @@
         <v>242.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>165.2828240682209</v>
+        <v>161.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -3388,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>547.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S36" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T36" t="n">
         <v>55.35776521751382</v>
@@ -3400,7 +3400,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>82.37314290982852</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>97.23431917176916</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3628,13 +3628,13 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S39" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T39" t="n">
         <v>55.35776521751382</v>
       </c>
       <c r="U39" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856292</v>
       </c>
       <c r="V39" t="n">
         <v>64.51066719152016</v>
@@ -3744,7 +3744,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>54.36328960686865</v>
+        <v>58.32868099228319</v>
       </c>
       <c r="F41" t="n">
         <v>54.88962870801186</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3820,7 +3820,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>262.0138729201192</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3874,7 +3874,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V42" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169627</v>
       </c>
       <c r="W42" t="n">
         <v>82.37314290982852</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -4099,19 +4099,19 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U45" t="n">
         <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169626</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
@@ -4297,49 +4297,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D2" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E2" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F2" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G2" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H2" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
       </c>
       <c r="J2" t="n">
-        <v>411.95</v>
+        <v>396.55</v>
       </c>
       <c r="K2" t="n">
-        <v>411.95</v>
+        <v>396.55</v>
       </c>
       <c r="L2" t="n">
-        <v>411.95</v>
+        <v>396.55</v>
       </c>
       <c r="M2" t="n">
-        <v>793.1</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>1174.25</v>
+        <v>1158.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="P2" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4348,25 +4348,25 @@
         <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4382,16 +4382,16 @@
         <v>722.3619790837812</v>
       </c>
       <c r="D3" t="n">
-        <v>596.2530132457184</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="E3" t="n">
-        <v>250.1195817084329</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="F3" t="n">
-        <v>250.1195817084329</v>
+        <v>379.2950676313803</v>
       </c>
       <c r="G3" t="n">
-        <v>250.1195817084329</v>
+        <v>379.2950676313803</v>
       </c>
       <c r="H3" t="n">
         <v>250.1195817084329</v>
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1247.586867406406</v>
+        <v>797.0710965443752</v>
       </c>
       <c r="C4" t="n">
-        <v>1373.588873224842</v>
+        <v>797.0710965443752</v>
       </c>
       <c r="D4" t="n">
-        <v>1486.908017349842</v>
+        <v>910.3902406693753</v>
       </c>
       <c r="E4" t="n">
-        <v>1486.908017349842</v>
+        <v>1028.219144880788</v>
       </c>
       <c r="F4" t="n">
-        <v>1486.908017349842</v>
+        <v>1152.580117472724</v>
       </c>
       <c r="G4" t="n">
-        <v>1540</v>
+        <v>1152.580117472724</v>
       </c>
       <c r="H4" t="n">
-        <v>1540</v>
+        <v>1152.580117472724</v>
       </c>
       <c r="I4" t="n">
-        <v>1540</v>
+        <v>1373.712996408807</v>
       </c>
       <c r="J4" t="n">
         <v>1540</v>
@@ -4485,22 +4485,22 @@
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
@@ -4509,22 +4509,22 @@
         <v>68.05025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>256.125934252978</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="U4" t="n">
-        <v>502.6771268912646</v>
+        <v>314.6014477324597</v>
       </c>
       <c r="V4" t="n">
-        <v>701.4985197772105</v>
+        <v>513.4228406184056</v>
       </c>
       <c r="W4" t="n">
-        <v>873.3894380368879</v>
+        <v>685.313758878083</v>
       </c>
       <c r="X4" t="n">
-        <v>1024.420229061081</v>
+        <v>685.313758878083</v>
       </c>
       <c r="Y4" t="n">
-        <v>1135.829529740114</v>
+        <v>685.313758878083</v>
       </c>
     </row>
     <row r="5">
@@ -4537,19 +4537,19 @@
         <v>141.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E5" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G5" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H5" t="n">
         <v>30.8</v>
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>722.3619790837812</v>
+        <v>541.0007750436882</v>
       </c>
       <c r="C6" t="n">
-        <v>722.3619790837812</v>
+        <v>541.0007750436882</v>
       </c>
       <c r="D6" t="n">
-        <v>722.3619790837812</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="E6" t="n">
-        <v>709.3902318427254</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="F6" t="n">
-        <v>366.3233203903244</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="G6" t="n">
-        <v>366.3233203903244</v>
+        <v>30.8</v>
       </c>
       <c r="H6" t="n">
         <v>30.8</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>862.6434684666581</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>795.4071048660406</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T6" t="n">
-        <v>789.9952208079459</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U6" t="n">
-        <v>789.7827362016966</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>775.1254966143025</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>742.4253522609404</v>
+        <v>561.0641482208474</v>
       </c>
       <c r="X6" t="n">
-        <v>722.3619790837812</v>
+        <v>541.0007750436882</v>
       </c>
       <c r="Y6" t="n">
-        <v>722.3619790837812</v>
+        <v>541.0007750436882</v>
       </c>
     </row>
     <row r="7">
@@ -4692,25 +4692,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42.98476868153026</v>
+        <v>672.9553827204466</v>
       </c>
       <c r="C7" t="n">
-        <v>168.986774499966</v>
+        <v>672.9553827204466</v>
       </c>
       <c r="D7" t="n">
-        <v>282.3059186249661</v>
+        <v>672.9553827204466</v>
       </c>
       <c r="E7" t="n">
-        <v>400.1348228363792</v>
+        <v>790.7842869318596</v>
       </c>
       <c r="F7" t="n">
-        <v>524.4957954283146</v>
+        <v>915.1452595237951</v>
       </c>
       <c r="G7" t="n">
-        <v>677.9023613151999</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="H7" t="n">
-        <v>847.4189464745974</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="I7" t="n">
         <v>1068.55182541068</v>
@@ -4743,25 +4743,25 @@
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>30.8</v>
+        <v>254.5132718224825</v>
       </c>
       <c r="U7" t="n">
-        <v>30.8</v>
+        <v>501.0644644607692</v>
       </c>
       <c r="V7" t="n">
-        <v>42.98476868153026</v>
+        <v>501.0644644607692</v>
       </c>
       <c r="W7" t="n">
-        <v>42.98476868153026</v>
+        <v>672.9553827204466</v>
       </c>
       <c r="X7" t="n">
-        <v>42.98476868153026</v>
+        <v>672.9553827204466</v>
       </c>
       <c r="Y7" t="n">
-        <v>42.98476868153026</v>
+        <v>672.9553827204466</v>
       </c>
     </row>
     <row r="8">
@@ -4789,28 +4789,28 @@
         <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="K8" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="L8" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="M8" t="n">
         <v>411.95</v>
       </c>
       <c r="N8" t="n">
-        <v>777.6999999999999</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="P8" t="n">
         <v>1540</v>
@@ -4856,16 +4856,16 @@
         <v>897.189519579215</v>
       </c>
       <c r="D9" t="n">
-        <v>720.0003429896865</v>
+        <v>897.189519579215</v>
       </c>
       <c r="E9" t="n">
-        <v>373.8669114524009</v>
+        <v>897.189519579215</v>
       </c>
       <c r="F9" t="n">
-        <v>30.8</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="G9" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H9" t="n">
         <v>30.8</v>
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1247.586867406406</v>
+        <v>850.0048837439258</v>
       </c>
       <c r="C10" t="n">
-        <v>1373.588873224842</v>
+        <v>976.0068895623616</v>
       </c>
       <c r="D10" t="n">
-        <v>1486.908017349842</v>
+        <v>976.0068895623616</v>
       </c>
       <c r="E10" t="n">
-        <v>1540</v>
+        <v>976.0068895623616</v>
       </c>
       <c r="F10" t="n">
-        <v>1540</v>
+        <v>1038.986101967658</v>
       </c>
       <c r="G10" t="n">
-        <v>1540</v>
+        <v>1038.986101967658</v>
       </c>
       <c r="H10" t="n">
-        <v>1540</v>
+        <v>1208.502687127056</v>
       </c>
       <c r="I10" t="n">
-        <v>1540</v>
+        <v>1429.635566063139</v>
       </c>
       <c r="J10" t="n">
-        <v>1540</v>
+        <v>1429.635566063139</v>
       </c>
       <c r="K10" t="n">
-        <v>1540</v>
+        <v>1540.000000000008</v>
       </c>
       <c r="L10" t="n">
         <v>1517.821760089168</v>
@@ -4986,19 +4986,19 @@
         <v>256.125934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>502.6771268912646</v>
+        <v>256.125934252978</v>
       </c>
       <c r="V10" t="n">
-        <v>701.4985197772105</v>
+        <v>454.9473271389239</v>
       </c>
       <c r="W10" t="n">
-        <v>873.3894380368879</v>
+        <v>626.8382453986013</v>
       </c>
       <c r="X10" t="n">
-        <v>1024.420229061081</v>
+        <v>626.8382453986013</v>
       </c>
       <c r="Y10" t="n">
-        <v>1135.829529740114</v>
+        <v>738.2475460776336</v>
       </c>
     </row>
     <row r="11">
@@ -5035,22 +5035,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L11" t="n">
-        <v>436.0291130376557</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M11" t="n">
-        <v>946.8779417665908</v>
+        <v>1682.59</v>
       </c>
       <c r="N11" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="O11" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="P11" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5087,16 +5087,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C12" t="n">
-        <v>390.8534315372855</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D12" t="n">
-        <v>390.8534315372855</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E12" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="F12" t="n">
         <v>44.72</v>
@@ -5263,31 +5263,31 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K14" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L14" t="n">
-        <v>989.4391130376558</v>
+        <v>1151.54</v>
       </c>
       <c r="M14" t="n">
-        <v>1243.990904947333</v>
+        <v>1151.54</v>
       </c>
       <c r="N14" t="n">
-        <v>1797.400904947332</v>
+        <v>1704.95</v>
       </c>
       <c r="O14" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P14" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5324,19 +5324,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="G15" t="n">
         <v>44.72</v>
@@ -5372,28 +5372,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S15" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C17" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D17" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E17" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F17" t="n">
         <v>157.615990899539</v>
@@ -5509,49 +5509,49 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L17" t="n">
         <v>989.4391130376558</v>
       </c>
       <c r="M17" t="n">
-        <v>1500.287941766591</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N17" t="n">
-        <v>2053.697941766591</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="O17" t="n">
-        <v>2236</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P17" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
       </c>
       <c r="R17" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S17" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V17" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W17" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X17" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y17" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C18" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D18" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E18" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F18" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="G18" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="H18" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5609,28 +5609,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S18" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T18" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U18" t="n">
-        <v>713.1992034391076</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V18" t="n">
-        <v>294.5015598113094</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W18" t="n">
-        <v>211.2963649528968</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X18" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y18" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="19">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C20" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D20" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E20" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F20" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G20" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H20" t="n">
         <v>44.72</v>
@@ -5746,49 +5746,49 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L20" t="n">
-        <v>436.0291130376557</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M20" t="n">
-        <v>946.8779417665908</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N20" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O20" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P20" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S20" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T20" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U20" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V20" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W20" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X20" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y20" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="21">
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>472.7782575464261</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C21" t="n">
-        <v>461.5662247731743</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D21" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E21" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F21" t="n">
         <v>44.72</v>
@@ -5864,10 +5864,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>557.5741660438614</v>
+        <v>492.1801502582655</v>
       </c>
       <c r="Y21" t="n">
-        <v>507.6838703204934</v>
+        <v>442.2898545348975</v>
       </c>
     </row>
     <row r="22">
@@ -5980,46 +5980,46 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K23" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="L23" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="M23" t="n">
-        <v>946.8779417665908</v>
+        <v>555.568828728935</v>
       </c>
       <c r="N23" t="n">
-        <v>1500.287941766591</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="O23" t="n">
-        <v>2053.697941766591</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="P23" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S23" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X23" t="n">
         <v>725.6800292188371</v>
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>409.4673863086053</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C24" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D24" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E24" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F24" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="G24" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="H24" t="n">
         <v>44.72</v>
@@ -6098,13 +6098,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X24" t="n">
-        <v>494.2632948060406</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y24" t="n">
-        <v>444.3729990826726</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="25">
@@ -6114,13 +6114,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C25" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D25" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E25" t="n">
         <v>1078.695883794875</v>
@@ -6168,22 +6168,22 @@
         <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X25" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y25" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="26">
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>626.8200754279619</v>
+        <v>632.3798821093615</v>
       </c>
       <c r="C26" t="n">
-        <v>494.0174711421095</v>
+        <v>499.577277823509</v>
       </c>
       <c r="D26" t="n">
-        <v>400.7455966574127</v>
+        <v>406.3054033388123</v>
       </c>
       <c r="E26" t="n">
-        <v>313.5099505898686</v>
+        <v>319.0697572712681</v>
       </c>
       <c r="F26" t="n">
-        <v>225.7426488646041</v>
+        <v>231.3024555460037</v>
       </c>
       <c r="G26" t="n">
         <v>144.6788471752802</v>
@@ -6220,16 +6220,16 @@
         <v>53.76</v>
       </c>
       <c r="K26" t="n">
-        <v>460.0517564436273</v>
+        <v>719.0399999999998</v>
       </c>
       <c r="L26" t="n">
-        <v>460.0517564436273</v>
+        <v>719.0399999999998</v>
       </c>
       <c r="M26" t="n">
-        <v>970.9005851725623</v>
+        <v>1229.888828728935</v>
       </c>
       <c r="N26" t="n">
-        <v>1584.120904947325</v>
+        <v>1843.109148503698</v>
       </c>
       <c r="O26" t="n">
         <v>2249.400904947332</v>
@@ -6262,7 +6262,7 @@
         <v>987.7460811232962</v>
       </c>
       <c r="Y26" t="n">
-        <v>792.4759471002594</v>
+        <v>798.035753781659</v>
       </c>
     </row>
     <row r="27">
@@ -6272,19 +6272,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>196.4403656206666</v>
+        <v>196.4403656206289</v>
       </c>
       <c r="C27" t="n">
-        <v>152.9051005241824</v>
+        <v>152.9051005241447</v>
       </c>
       <c r="D27" t="n">
-        <v>122.6650127487252</v>
+        <v>122.6650127486875</v>
       </c>
       <c r="E27" t="n">
-        <v>97.74370242356093</v>
+        <v>97.74370242352325</v>
       </c>
       <c r="F27" t="n">
-        <v>75.88891218328128</v>
+        <v>75.88891218324358</v>
       </c>
       <c r="G27" t="n">
         <v>68.07119917820316</v>
@@ -6317,31 +6317,31 @@
         <v>1209.192420368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>1214.723619351867</v>
+        <v>1214.723619351829</v>
       </c>
       <c r="R27" t="n">
-        <v>983.1339251171403</v>
+        <v>983.1339251171026</v>
       </c>
       <c r="S27" t="n">
-        <v>833.0692786882399</v>
+        <v>833.0692786882023</v>
       </c>
       <c r="T27" t="n">
-        <v>744.8291118018624</v>
+        <v>744.8291118018248</v>
       </c>
       <c r="U27" t="n">
-        <v>661.7883443673303</v>
+        <v>661.7883443672927</v>
       </c>
       <c r="V27" t="n">
-        <v>564.3028219516534</v>
+        <v>564.3028219516158</v>
       </c>
       <c r="W27" t="n">
-        <v>448.7743947700085</v>
+        <v>448.7743947699708</v>
       </c>
       <c r="X27" t="n">
-        <v>345.8827387645665</v>
+        <v>345.8827387645288</v>
       </c>
       <c r="Y27" t="n">
-        <v>263.6692107179662</v>
+        <v>263.6692107179285</v>
       </c>
     </row>
     <row r="28">
@@ -6381,25 +6381,25 @@
         <v>1431.431843630702</v>
       </c>
       <c r="L28" t="n">
-        <v>1431.431843630702</v>
+        <v>1324.818077814764</v>
       </c>
       <c r="M28" t="n">
-        <v>1431.431843630702</v>
+        <v>1120.139682458653</v>
       </c>
       <c r="N28" t="n">
-        <v>1431.431843630702</v>
+        <v>864.3971821842238</v>
       </c>
       <c r="O28" t="n">
-        <v>1251.627971449522</v>
+        <v>538.6945922054208</v>
       </c>
       <c r="P28" t="n">
-        <v>878.4482771785345</v>
+        <v>511.3111188727339</v>
       </c>
       <c r="Q28" t="n">
-        <v>466.4894222031829</v>
+        <v>511.3111188727339</v>
       </c>
       <c r="R28" t="n">
-        <v>53.76</v>
+        <v>98.58169666955095</v>
       </c>
       <c r="S28" t="n">
         <v>53.76</v>
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>632.3798821093615</v>
+        <v>626.8200754279619</v>
       </c>
       <c r="C29" t="n">
-        <v>499.577277823509</v>
+        <v>494.0174711421095</v>
       </c>
       <c r="D29" t="n">
-        <v>406.3054033388123</v>
+        <v>400.7455966574127</v>
       </c>
       <c r="E29" t="n">
-        <v>319.0697572712681</v>
+        <v>313.5099505898686</v>
       </c>
       <c r="F29" t="n">
-        <v>231.3024555460037</v>
+        <v>225.7426488646041</v>
       </c>
       <c r="G29" t="n">
         <v>144.6788471752802</v>
@@ -6466,10 +6466,10 @@
         <v>955.9179417665907</v>
       </c>
       <c r="N29" t="n">
-        <v>1569.138261541354</v>
+        <v>955.9179417665907</v>
       </c>
       <c r="O29" t="n">
-        <v>2234.418261541349</v>
+        <v>1584.120904947338</v>
       </c>
       <c r="P29" t="n">
         <v>2249.400904947332</v>
@@ -6499,7 +6499,7 @@
         <v>987.7460811232962</v>
       </c>
       <c r="Y29" t="n">
-        <v>798.035753781659</v>
+        <v>792.4759471002594</v>
       </c>
     </row>
     <row r="30">
@@ -6530,28 +6530,28 @@
         <v>53.76</v>
       </c>
       <c r="I30" t="n">
-        <v>53.76</v>
+        <v>59.29119898333113</v>
       </c>
       <c r="J30" t="n">
-        <v>177.7165201752989</v>
+        <v>183.2477191586301</v>
       </c>
       <c r="K30" t="n">
-        <v>366.9093362696823</v>
+        <v>372.4405352530135</v>
       </c>
       <c r="L30" t="n">
-        <v>638.2597978648824</v>
+        <v>643.7909968482136</v>
       </c>
       <c r="M30" t="n">
-        <v>724.3403396077417</v>
+        <v>729.8715385910729</v>
       </c>
       <c r="N30" t="n">
-        <v>857.62062421531</v>
+        <v>863.1518231986412</v>
       </c>
       <c r="O30" t="n">
-        <v>1096.663075899029</v>
+        <v>1102.19427488236</v>
       </c>
       <c r="P30" t="n">
-        <v>1209.192420368536</v>
+        <v>1214.723619351867</v>
       </c>
       <c r="Q30" t="n">
         <v>1214.723619351867</v>
@@ -6621,19 +6621,19 @@
         <v>1431.431843630702</v>
       </c>
       <c r="M31" t="n">
-        <v>1431.431843630702</v>
+        <v>1226.753448274591</v>
       </c>
       <c r="N31" t="n">
-        <v>1431.431843630702</v>
+        <v>971.0109480001622</v>
       </c>
       <c r="O31" t="n">
-        <v>1105.729253651899</v>
+        <v>645.3083580213593</v>
       </c>
       <c r="P31" t="n">
-        <v>732.5495593809121</v>
+        <v>272.1286637503719</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.4894222031829</v>
+        <v>272.1286637503719</v>
       </c>
       <c r="R31" t="n">
         <v>53.76</v>
@@ -6691,31 +6691,31 @@
         <v>53.76</v>
       </c>
       <c r="J32" t="n">
-        <v>53.76</v>
+        <v>233.3708514962635</v>
       </c>
       <c r="K32" t="n">
-        <v>53.76</v>
+        <v>233.3708514962635</v>
       </c>
       <c r="L32" t="n">
-        <v>719.0399999999998</v>
+        <v>898.6508514962635</v>
       </c>
       <c r="M32" t="n">
-        <v>1229.888828728935</v>
+        <v>1409.499680225199</v>
       </c>
       <c r="N32" t="n">
-        <v>1843.109148503698</v>
+        <v>2022.719999999962</v>
       </c>
       <c r="O32" t="n">
-        <v>1843.109148503698</v>
+        <v>2688</v>
       </c>
       <c r="P32" t="n">
-        <v>2249.400904947332</v>
+        <v>2688</v>
       </c>
       <c r="Q32" t="n">
         <v>2688</v>
       </c>
       <c r="R32" t="n">
-        <v>2688.000000000088</v>
+        <v>2688</v>
       </c>
       <c r="S32" t="n">
         <v>2514.92529374976</v>
@@ -6767,34 +6767,34 @@
         <v>53.76</v>
       </c>
       <c r="I33" t="n">
-        <v>59.29119898333113</v>
+        <v>53.76</v>
       </c>
       <c r="J33" t="n">
-        <v>183.2477191586301</v>
+        <v>177.7165201752989</v>
       </c>
       <c r="K33" t="n">
-        <v>372.4405352530135</v>
+        <v>366.9093362696823</v>
       </c>
       <c r="L33" t="n">
-        <v>643.7909968482136</v>
+        <v>638.2597978648824</v>
       </c>
       <c r="M33" t="n">
-        <v>729.8715385910729</v>
+        <v>724.3403396077417</v>
       </c>
       <c r="N33" t="n">
-        <v>863.1518231986412</v>
+        <v>857.62062421531</v>
       </c>
       <c r="O33" t="n">
-        <v>1102.19427488236</v>
+        <v>1096.663075899029</v>
       </c>
       <c r="P33" t="n">
-        <v>1214.723619351867</v>
+        <v>1209.192420368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>1214.723619351867</v>
+        <v>1214.723619351843</v>
       </c>
       <c r="R33" t="n">
-        <v>983.1339251171403</v>
+        <v>983.1339251171169</v>
       </c>
       <c r="S33" t="n">
         <v>833.0692786882399</v>
@@ -6855,25 +6855,25 @@
         <v>1431.431843630702</v>
       </c>
       <c r="L34" t="n">
-        <v>1431.431843630702</v>
+        <v>1324.818077814764</v>
       </c>
       <c r="M34" t="n">
-        <v>1431.431843630702</v>
+        <v>1120.139682458653</v>
       </c>
       <c r="N34" t="n">
-        <v>1175.689343356273</v>
+        <v>1120.139682458653</v>
       </c>
       <c r="O34" t="n">
-        <v>849.9867533774702</v>
+        <v>794.43709247985</v>
       </c>
       <c r="P34" t="n">
-        <v>849.9867533774702</v>
+        <v>511.3111188727339</v>
       </c>
       <c r="Q34" t="n">
-        <v>438.0278984021187</v>
+        <v>511.3111188727339</v>
       </c>
       <c r="R34" t="n">
-        <v>53.76</v>
+        <v>98.58169666955095</v>
       </c>
       <c r="S34" t="n">
         <v>53.76</v>
@@ -6928,19 +6928,19 @@
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>137.1709049473328</v>
+        <v>44.72</v>
       </c>
       <c r="K35" t="n">
-        <v>690.5809049473327</v>
+        <v>44.72</v>
       </c>
       <c r="L35" t="n">
+        <v>598.13</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1108.978828728935</v>
+      </c>
+      <c r="N35" t="n">
         <v>1243.990904947333</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1243.990904947333</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1797.400904947332</v>
       </c>
       <c r="O35" t="n">
         <v>1797.400904947332</v>
@@ -6952,25 +6952,25 @@
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y35" t="n">
         <v>562.7331275190327</v>
@@ -7031,16 +7031,16 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>647.3506049216877</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S36" t="n">
-        <v>466.2983195781991</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T36" t="n">
-        <v>410.3813850150538</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U36" t="n">
-        <v>359.6638499037541</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V36" t="n">
         <v>294.5015598113094</v>
@@ -7062,13 +7062,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E37" t="n">
         <v>1078.695883794875</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7165,16 +7165,16 @@
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K38" t="n">
-        <v>989.4391130376558</v>
+        <v>598.13</v>
       </c>
       <c r="L38" t="n">
-        <v>1286.552076218397</v>
+        <v>1151.54</v>
       </c>
       <c r="M38" t="n">
-        <v>1797.400904947332</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N38" t="n">
         <v>1797.400904947332</v>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>409.4673863086053</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
         <v>44.72</v>
@@ -7271,25 +7271,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F40" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G40" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H40" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I40" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J40" t="n">
         <v>1860.696627021627</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
         <v>213.0600603015712</v>
@@ -7405,49 +7405,49 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M41" t="n">
-        <v>946.8779417665908</v>
+        <v>1129.18</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.287941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>407.3842417608302</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
-        <v>396.1722089875784</v>
+        <v>44.72</v>
       </c>
       <c r="D42" t="n">
         <v>44.72</v>
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>935.4919426714454</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>817.7505285657774</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>761.8335940026321</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>711.1160588913324</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>645.9537687988877</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W42" t="n">
-        <v>562.7485739404751</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X42" t="n">
-        <v>492.1801502582655</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y42" t="n">
-        <v>442.2898545348975</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C43" t="n">
         <v>946.5478354584615</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U43" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V43" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W43" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X43" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y43" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="44">
@@ -7639,25 +7639,25 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K44" t="n">
-        <v>989.4391130376558</v>
+        <v>598.13</v>
       </c>
       <c r="L44" t="n">
-        <v>1542.849113037656</v>
+        <v>598.13</v>
       </c>
       <c r="M44" t="n">
-        <v>1542.849113037656</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N44" t="n">
-        <v>1542.849113037656</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="O44" t="n">
-        <v>2096.259113037656</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7742,16 +7742,16 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>466.2983195781991</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T45" t="n">
-        <v>410.3813850150538</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U45" t="n">
-        <v>359.6638499037541</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V45" t="n">
         <v>294.5015598113094</v>
@@ -7773,28 +7773,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C46" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D46" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E46" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F46" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G46" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H46" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I46" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J46" t="n">
         <v>1860.696627021627</v>
@@ -7827,22 +7827,22 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U46" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V46" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W46" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X46" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y46" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>420.0430062450903</v>
+        <v>404.4874506895348</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7979,13 +7979,13 @@
         <v>862.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>439.6923140185369</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P2" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
-        <v>172.8226843274854</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8447,16 +8447,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>846.6934025142796</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
         <v>455.2478695740924</v>
       </c>
       <c r="P8" t="n">
-        <v>385.2870600406814</v>
+        <v>369.7315044851259</v>
       </c>
       <c r="Q8" t="n">
         <v>172.8226843274854</v>
@@ -8678,10 +8678,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>184.14349316506</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,13 +8690,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>356.9661774925453</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>801.385149773304</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N14" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>606.6620109882336</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,25 +9152,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>559</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N17" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O17" t="n">
-        <v>254.3913627391524</v>
+        <v>327.3708917050791</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,25 +9389,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>777.3630622928068</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9641,10 +9641,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>136.6628946047192</v>
       </c>
       <c r="Q23" t="n">
-        <v>356.9661774925453</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,7 +9863,7 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>410.3957135794215</v>
+        <v>672</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9875,7 +9875,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>742.2478695740995</v>
+        <v>480.643583153521</v>
       </c>
       <c r="P26" t="n">
         <v>0.2870600406814136</v>
@@ -10109,13 +10109,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O29" t="n">
-        <v>742.2478695740876</v>
+        <v>704.7963172314127</v>
       </c>
       <c r="P29" t="n">
-        <v>15.42104327904834</v>
+        <v>672.2870600406761</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>216.4681087665687</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10349,13 +10349,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>70.24786957409245</v>
+        <v>742.2478695741313</v>
       </c>
       <c r="P32" t="n">
-        <v>410.68277362011</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,22 +10571,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>128.4277587171436</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>613.6247926338732</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>300.1141042229713</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>613.624792633873</v>
       </c>
       <c r="O38" t="n">
         <v>70.24786957409245</v>
@@ -11048,25 +11048,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>685.4145387153925</v>
       </c>
       <c r="N41" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>370.3619737970638</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,16 +11282,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
         <v>477.2489580698352</v>
@@ -11300,10 +11300,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>141.4394711137563</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>193.2279078336117</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646055957</v>
+        <v>1.591170646048568</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5.504208614585579</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>5.504208614585508</v>
       </c>
     </row>
     <row r="27">
@@ -24596,28 +24596,28 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>105.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>202.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>253.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>144.4397306196462</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>342.3382587289174</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>407.839266425598</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>44.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5.504208614585579</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24714,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.504208614585508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24836,10 +24836,10 @@
         <v>105.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>202.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>253.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -24848,10 +24848,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>144.4397306196461</v>
+        <v>407.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>192.4171508682828</v>
       </c>
       <c r="S31" t="n">
         <v>44.37347970285543</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>5.504208614498793</v>
+        <v>5.504208614585679</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25070,28 +25070,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>105.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>202.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>253.1850752716849</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>369.4478973282775</v>
+        <v>89.15318345723256</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>407.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>28.17690856305353</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>44.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8555623.865124457</v>
+        <v>8555623.865124455</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9486324.848666826</v>
+        <v>9486324.848666824</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10417025.83220921</v>
+        <v>10417025.8322092</v>
       </c>
     </row>
     <row r="13">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13245281.80689696</v>
+        <v>13245281.80689695</v>
       </c>
     </row>
     <row r="16">
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1259338.85223709</v>
+        <v>1259338.852237089</v>
       </c>
       <c r="C2" t="n">
         <v>1259338.85223709</v>
@@ -26281,7 +26281,7 @@
         <v>1259377.040332595</v>
       </c>
       <c r="F2" t="n">
-        <v>1259377.040332596</v>
+        <v>1259377.040332594</v>
       </c>
       <c r="G2" t="n">
         <v>1259377.040332595</v>
@@ -26290,7 +26290,7 @@
         <v>1259377.040332595</v>
       </c>
       <c r="I2" t="n">
-        <v>1259377.040332595</v>
+        <v>1259377.040332596</v>
       </c>
       <c r="J2" t="n">
         <v>1240934.644723166</v>
@@ -26299,7 +26299,7 @@
         <v>1240934.644723166</v>
       </c>
       <c r="L2" t="n">
-        <v>1240934.644723173</v>
+        <v>1240934.644723166</v>
       </c>
       <c r="M2" t="n">
         <v>1259377.040332595</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941388</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>509242.089049618</v>
+        <v>511130.7051621593</v>
       </c>
       <c r="K4" t="n">
-        <v>507410.0945171365</v>
+        <v>509298.7106296779</v>
       </c>
       <c r="L4" t="n">
-        <v>505575.4970691528</v>
+        <v>507464.1131816903</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421008</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>495869.1273375804</v>
+        <v>494353.2716492644</v>
       </c>
       <c r="C6" t="n">
-        <v>633447.1074713949</v>
+        <v>631931.2517830789</v>
       </c>
       <c r="D6" t="n">
-        <v>635507.8793837108</v>
+        <v>633992.0236953947</v>
       </c>
       <c r="E6" t="n">
-        <v>311623.6371060599</v>
+        <v>309881.7872929518</v>
       </c>
       <c r="F6" t="n">
-        <v>654814.5324515646</v>
+        <v>653072.6826384556</v>
       </c>
       <c r="G6" t="n">
-        <v>656760.1089197499</v>
+        <v>655018.259106642</v>
       </c>
       <c r="H6" t="n">
-        <v>658708.3857370511</v>
+        <v>656966.5359239435</v>
       </c>
       <c r="I6" t="n">
-        <v>660659.3823804111</v>
+        <v>658917.5325673042</v>
       </c>
       <c r="J6" t="n">
-        <v>234405.013673548</v>
+        <v>232516.3975610069</v>
       </c>
       <c r="K6" t="n">
-        <v>665933.0082060295</v>
+        <v>664044.3920934879</v>
       </c>
       <c r="L6" t="n">
-        <v>667767.6056540202</v>
+        <v>665878.9895414759</v>
       </c>
       <c r="M6" t="n">
-        <v>621418.9657904941</v>
+        <v>619677.1159773868</v>
       </c>
       <c r="N6" t="n">
-        <v>670455.8628253479</v>
+        <v>668714.0130122405</v>
       </c>
       <c r="O6" t="n">
-        <v>418023.6020830863</v>
+        <v>416281.7522699783</v>
       </c>
       <c r="P6" t="n">
-        <v>674394.2049340956</v>
+        <v>672652.355120988</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27008,7 +27008,7 @@
         <v>32</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>318</v>
@@ -27045,10 +27045,10 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>61</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27518,19 +27518,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>223.0898107180205</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>204.2843561227032</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27594,28 +27594,28 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>298.6721381447203</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>203.2356191300424</v>
       </c>
       <c r="K4" t="n">
         <v>288.520773801143</v>
@@ -27645,7 +27645,7 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
@@ -27657,10 +27657,10 @@
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27673,7 +27673,7 @@
         <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="D5" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -27755,19 +27755,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>168.5784554794787</v>
       </c>
       <c r="E6" t="n">
-        <v>329.8300674532674</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27812,7 +27812,7 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>47.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27831,10 +27831,10 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
@@ -27846,10 +27846,10 @@
         <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
         <v>400</v>
@@ -27879,19 +27879,19 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>398.3710480500046</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>211.4781573692771</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27992,19 +27992,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>172.5204020740694</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>139.8182410159025</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28071,28 +28071,28 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>334.6091701401468</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>337.9982220336983</v>
       </c>
       <c r="G10" t="n">
         <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28122,7 +28122,7 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
@@ -28131,7 +28131,7 @@
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28223,19 +28223,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>279.99433469647</v>
+        <v>350</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>276.9584798124343</v>
       </c>
       <c r="G12" t="n">
         <v>325.7395358750273</v>
@@ -28399,10 +28399,10 @@
         <v>350</v>
       </c>
       <c r="H14" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28466,7 +28466,7 @@
         <v>350</v>
       </c>
       <c r="D15" t="n">
-        <v>260.9994602472874</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>342.6720972219126</v>
@@ -28475,7 +28475,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
         <v>332.1680871864211</v>
@@ -28508,7 +28508,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S15" t="n">
         <v>350</v>
@@ -28529,7 +28529,7 @@
         <v>350</v>
       </c>
       <c r="Y15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28630,7 +28630,7 @@
         <v>350</v>
       </c>
       <c r="F17" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G17" t="n">
         <v>350</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
         <v>350</v>
@@ -28718,7 +28718,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>154.4486233659061</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28745,7 +28745,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>350</v>
@@ -28754,10 +28754,10 @@
         <v>350</v>
       </c>
       <c r="U18" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W18" t="n">
         <v>350</v>
@@ -28873,7 +28873,7 @@
         <v>350</v>
       </c>
       <c r="H20" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I20" t="n">
         <v>150.0811596826846</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28940,13 +28940,13 @@
         <v>350</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>325.7395358750273</v>
@@ -29000,7 +29000,7 @@
         <v>350</v>
       </c>
       <c r="X21" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="Y21" t="n">
         <v>350</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29158,7 +29158,7 @@
         <v>350</v>
       </c>
       <c r="X23" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="Y23" t="n">
         <v>350</v>
@@ -29174,7 +29174,7 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -29189,7 +29189,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>332.1680871864211</v>
+        <v>269.4903246609787</v>
       </c>
       <c r="I24" t="n">
         <v>217.1263858913485</v>
@@ -29234,10 +29234,10 @@
         <v>350</v>
       </c>
       <c r="W24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="Y24" t="n">
         <v>350</v>
@@ -29259,7 +29259,7 @@
         <v>350</v>
       </c>
       <c r="E25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="F25" t="n">
         <v>350</v>
@@ -29304,7 +29304,7 @@
         <v>350</v>
       </c>
       <c r="T25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U25" t="n">
         <v>350</v>
@@ -29423,7 +29423,7 @@
         <v>318</v>
       </c>
       <c r="G27" t="n">
-        <v>318</v>
+        <v>318.0000000000373</v>
       </c>
       <c r="H27" t="n">
         <v>318</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>178.6663347706119</v>
+        <v>178.6663347705741</v>
       </c>
       <c r="R27" t="n">
         <v>318</v>
@@ -29666,7 +29666,7 @@
         <v>318</v>
       </c>
       <c r="I30" t="n">
-        <v>217.1263858913485</v>
+        <v>222.713455571481</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>178.6663347706119</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
         <v>318</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>250.8785988283831</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
         <v>318</v>
@@ -29903,7 +29903,7 @@
         <v>318</v>
       </c>
       <c r="I33" t="n">
-        <v>222.713455571481</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,13 +29927,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>173.0792650904796</v>
+        <v>178.6663347705883</v>
       </c>
       <c r="R33" t="n">
         <v>318</v>
       </c>
       <c r="S33" t="n">
-        <v>318</v>
+        <v>318.0000000000232</v>
       </c>
       <c r="T33" t="n">
         <v>318</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30109,7 +30109,7 @@
         <v>350</v>
       </c>
       <c r="Y35" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36">
@@ -30167,10 +30167,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S36" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T36" t="n">
         <v>350</v>
@@ -30179,7 +30179,7 @@
         <v>350</v>
       </c>
       <c r="V36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>350</v>
@@ -30207,7 +30207,7 @@
         <v>350</v>
       </c>
       <c r="E37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="F37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30407,13 +30407,13 @@
         <v>350</v>
       </c>
       <c r="S39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>350</v>
       </c>
       <c r="U39" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="V39" t="n">
         <v>350</v>
@@ -30459,7 +30459,7 @@
         <v>350</v>
       </c>
       <c r="J40" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30523,7 +30523,7 @@
         <v>350</v>
       </c>
       <c r="E41" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="F41" t="n">
         <v>350</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30599,7 +30599,7 @@
         <v>350</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>342.6720972219126</v>
@@ -30641,7 +30641,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>285.25992437226</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30653,7 +30653,7 @@
         <v>350</v>
       </c>
       <c r="V42" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="W42" t="n">
         <v>350</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -30675,58 +30675,58 @@
         <v>350</v>
       </c>
       <c r="C43" t="n">
+        <v>350</v>
+      </c>
+      <c r="D43" t="n">
+        <v>350</v>
+      </c>
+      <c r="E43" t="n">
+        <v>350</v>
+      </c>
+      <c r="F43" t="n">
+        <v>350</v>
+      </c>
+      <c r="G43" t="n">
+        <v>350</v>
+      </c>
+      <c r="H43" t="n">
+        <v>350</v>
+      </c>
+      <c r="I43" t="n">
+        <v>350</v>
+      </c>
+      <c r="J43" t="n">
+        <v>350</v>
+      </c>
+      <c r="K43" t="n">
+        <v>350</v>
+      </c>
+      <c r="L43" t="n">
+        <v>350</v>
+      </c>
+      <c r="M43" t="n">
+        <v>350</v>
+      </c>
+      <c r="N43" t="n">
+        <v>350</v>
+      </c>
+      <c r="O43" t="n">
+        <v>350</v>
+      </c>
+      <c r="P43" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>350</v>
+      </c>
+      <c r="R43" t="n">
+        <v>350</v>
+      </c>
+      <c r="S43" t="n">
+        <v>350</v>
+      </c>
+      <c r="T43" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="D43" t="n">
-        <v>350</v>
-      </c>
-      <c r="E43" t="n">
-        <v>350</v>
-      </c>
-      <c r="F43" t="n">
-        <v>350</v>
-      </c>
-      <c r="G43" t="n">
-        <v>350</v>
-      </c>
-      <c r="H43" t="n">
-        <v>350</v>
-      </c>
-      <c r="I43" t="n">
-        <v>350</v>
-      </c>
-      <c r="J43" t="n">
-        <v>350</v>
-      </c>
-      <c r="K43" t="n">
-        <v>350</v>
-      </c>
-      <c r="L43" t="n">
-        <v>350</v>
-      </c>
-      <c r="M43" t="n">
-        <v>350</v>
-      </c>
-      <c r="N43" t="n">
-        <v>350</v>
-      </c>
-      <c r="O43" t="n">
-        <v>350</v>
-      </c>
-      <c r="P43" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>350</v>
-      </c>
-      <c r="R43" t="n">
-        <v>350</v>
-      </c>
-      <c r="S43" t="n">
-        <v>350</v>
-      </c>
-      <c r="T43" t="n">
-        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30878,19 +30878,19 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S45" t="n">
+        <v>350</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>350</v>
+      </c>
+      <c r="V45" t="n">
         <v>287.3222374745576</v>
-      </c>
-      <c r="T45" t="n">
-        <v>350</v>
-      </c>
-      <c r="U45" t="n">
-        <v>350</v>
-      </c>
-      <c r="V45" t="n">
-        <v>350</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
@@ -30933,7 +30933,7 @@
         <v>350</v>
       </c>
       <c r="J46" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K46" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34758,13 +34758,13 @@
         <v>385</v>
       </c>
       <c r="O2" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,28 +34880,28 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>53.62826530319025</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>167.9666702941346</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34931,7 +34931,7 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
@@ -34943,10 +34943,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -35117,10 +35117,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
@@ -35132,10 +35132,10 @@
         <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>364.7310511640923</v>
@@ -35165,19 +35165,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>188.3464815437469</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>12.30784715306086</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35217,25 +35217,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>385</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="O8" t="n">
         <v>385</v>
       </c>
       <c r="P8" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35357,28 +35357,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>53.62826530319025</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>63.6153660659564</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35408,7 +35408,7 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
@@ -35417,7 +35417,7 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35457,10 +35457,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>184.14349316506</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,13 +35469,13 @@
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>257.1230221309867</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>536.4141414141411</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35931,25 +35931,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>559</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>257.1230221309867</v>
+      </c>
+      <c r="P17" t="n">
         <v>559</v>
       </c>
-      <c r="O17" t="n">
-        <v>184.1434931650599</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36168,25 +36168,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>300.1141042229716</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,7 +36402,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -36420,10 +36420,10 @@
         <v>559</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="Q23" t="n">
-        <v>184.1434931650599</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36545,7 +36545,7 @@
         <v>64.46378194444452</v>
       </c>
       <c r="E25" t="n">
-        <v>69.01909516304346</v>
+        <v>61.23042579717762</v>
       </c>
       <c r="F25" t="n">
         <v>75.61714403225807</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U25" t="n">
         <v>199.0416087255421</v>
@@ -36642,7 +36642,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>410.3957135794215</v>
+        <v>672</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -36654,7 +36654,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>672.000000000007</v>
+        <v>410.3957135794286</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.587069680132347</v>
+        <v>5.587069680094451</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36888,13 +36888,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>671.9999999999952</v>
+        <v>634.5484476573203</v>
       </c>
       <c r="P29" t="n">
-        <v>15.13398323836692</v>
+        <v>671.9999999999947</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>5.587069680132455</v>
       </c>
       <c r="J30" t="n">
         <v>125.2086062376757</v>
@@ -36976,7 +36976,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.587069680132347</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,7 +37113,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>181.4251025214784</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -37128,16 +37128,16 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>672.0000000000389</v>
       </c>
       <c r="P32" t="n">
-        <v>410.3957135794286</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>8.865276638493694e-11</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>5.587069680132455</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37213,7 +37213,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5.587069680108691</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37350,22 +37350,22 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
+        <v>136.375834564038</v>
+      </c>
+      <c r="O35" t="n">
         <v>559</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37493,7 +37493,7 @@
         <v>64.46378194444452</v>
       </c>
       <c r="E37" t="n">
-        <v>69.01909516304346</v>
+        <v>61.23042579717762</v>
       </c>
       <c r="F37" t="n">
         <v>75.61714403225807</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>300.1141042229713</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J40" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
         <v>61.47922619885696</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37827,25 +37827,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>141.1524110730752</v>
       </c>
       <c r="N41" t="n">
         <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37961,7 +37961,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C43" t="n">
-        <v>69.48608398608951</v>
+        <v>77.27475335195533</v>
       </c>
       <c r="D43" t="n">
         <v>64.46378194444452</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,16 +38061,16 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>559</v>
       </c>
       <c r="P44" t="n">
-        <v>141.1524110730749</v>
+        <v>559</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>20.40522350612631</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J46" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K46" t="n">
         <v>61.47922619885696</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
